--- a/assets/assets/pliki_bazy/polecane.xlsx
+++ b/assets/assets/pliki_bazy/polecane.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\pliki_bazy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\assets\pliki_bazy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371C9136-6245-4A63-98B9-E50BCCD7F0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4959A5-A74B-4743-935D-8966A9F7A398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30870" yWindow="5715" windowWidth="20280" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31830" yWindow="2400" windowWidth="23055" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -521,7 +521,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="4">
-        <v>45812</v>
+        <v>45753</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
